--- a/artfynd/A 60085-2021 artfynd.xlsx
+++ b/artfynd/A 60085-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60085-2021 artfynd.xlsx
+++ b/artfynd/A 60085-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70084884</v>
+        <v>70084851</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472672.9429048626</v>
+        <v>472640</v>
       </c>
       <c r="R2" t="n">
-        <v>6587973.952844339</v>
+        <v>6587954</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2017-05-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blandskog, bäckravin</t>
+          <t>Örtgranskog i bäckdal</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fuktig mark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,12 +789,7 @@
         <v>70084834</v>
       </c>
       <c r="B3" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472679.9786396976</v>
+        <v>472680</v>
       </c>
       <c r="R3" t="n">
-        <v>6587960.164502659</v>
+        <v>6587960</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,19 +854,9 @@
           <t>2017-05-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,50 +897,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>70084851</v>
+        <v>109436750</v>
       </c>
       <c r="B4" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>5749</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Citronfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Ramaria gypsea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Trösälven, Vrm</t>
+          <t>V om Trösälven, N om Tavlan, Karlskoga kommun, Tavlan-området, N Kga, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472640.1776487186</v>
+        <v>472623</v>
       </c>
       <c r="R4" t="n">
-        <v>6587953.838394742</v>
+        <v>6587893</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,22 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-05-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-10-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,47 +987,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Örtgranskog i bäckdal</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Fuktig mark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Lennart Söderberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Lennart Söderberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73077423</v>
+        <v>70084884</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,31 +1034,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pålsäng, NNV om, Vrm</t>
+          <t>Trösälven, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472652.0640432112</v>
+        <v>472673</v>
       </c>
       <c r="R5" t="n">
-        <v>6587835.709939096</v>
+        <v>6587974</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1132,22 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-06-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-05-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-06-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,83 +1090,81 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Granskog, f.d. åkermark.</t>
+          <t>Blandskog, bäckravin</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Trösan Stockforsen - Tallfallet</t>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109436750</v>
+        <v>73077423</v>
       </c>
       <c r="B6" t="n">
-        <v>88945</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5749</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Citronfingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria schildii</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>V om Trösälven, N om Tavlan, Karlskoga kommun, Tavlan-området, N Kga, Vrm</t>
+          <t>Pålsäng, NNV om, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472623.4296568211</v>
+        <v>472652</v>
       </c>
       <c r="R6" t="n">
-        <v>6587893.412680847</v>
+        <v>6587836</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1264,22 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,22 +1205,30 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Granskog, f.d. åkermark.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lennart Söderberg</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lennart Söderberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trösan Stockforsen - Tallfallet</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60085-2021 artfynd.xlsx
+++ b/artfynd/A 60085-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70084851</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70084834</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109436750</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70084884</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,8 +1254,20 @@
           <t>Trösan Stockforsen - Tallfallet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73077423</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>